--- a/intermidiate_tables_csv/06_top_ga_features.xlsx
+++ b/intermidiate_tables_csv/06_top_ga_features.xlsx
@@ -443,101 +443,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>elite_nn.max</t>
+          <t>mut_inf.max</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>best_node.max</t>
+          <t>one_nn.max</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>best_node.min</t>
+          <t>attr_conc.sd</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>can_cor.sd</t>
+          <t>mean.min</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>eigenvalues.min</t>
+          <t>one_nn.min</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>linear_discr.sd</t>
+          <t>elite_nn.min</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>nr_outliers</t>
+          <t>cor.min</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>one_nn.min</t>
+          <t>cov.min</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>iq_range.min</t>
+          <t>kurtosis.mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>can_cor.min</t>
+          <t>nr_outliers</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/intermidiate_tables_csv/06_top_ga_features.xlsx
+++ b/intermidiate_tables_csv/06_top_ga_features.xlsx
@@ -443,7 +443,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mut_inf.max</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>one_nn.max</t>
+          <t>cor.kurtosis</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -463,21 +463,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>attr_conc.sd</t>
+          <t>leaves_corrob.kurtosis</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mean.min</t>
+          <t>mut_inf.max</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>elite_nn.min</t>
+          <t>attr_conc.kurtosis</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -503,41 +503,41 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cor.min</t>
+          <t>attr_conc.mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cov.min</t>
+          <t>cor.mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kurtosis.mean</t>
+          <t>impconceptvar.kurtosis</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>nr_outliers</t>
+          <t>joint_ent.kurtosis</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/intermidiate_tables_csv/06_top_ga_features.xlsx
+++ b/intermidiate_tables_csv/06_top_ga_features.xlsx
@@ -443,101 +443,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mut_inf.max</t>
+          <t>l2.max</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>one_nn.max</t>
+          <t>one_itemset.iq_range</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>attr_conc.sd</t>
+          <t>one_nn.max</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mean.min</t>
+          <t>one_nn.min</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>one_nn.min</t>
+          <t>two_itemset.histogram.9</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>elite_nn.min</t>
+          <t>attr_ent.quantiles.3</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cor.min</t>
+          <t>attr_to_inst</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cov.min</t>
+          <t>ch</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kurtosis.mean</t>
+          <t>cor.mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>nr_outliers</t>
+          <t>eigenvalues.iq_range</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
